--- a/xlsx/Power/pgroups3.xlsx
+++ b/xlsx/Power/pgroups3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B82C4A2-5880-445A-9043-095FEA92FFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F672E7FF-B853-4818-B0F1-7D5E0709655D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{FCA0BD69-1097-4BD5-987D-1F380216A0FD}"/>
+    <workbookView xWindow="4485" yWindow="3945" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{FCA0BD69-1097-4BD5-987D-1F380216A0FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,60 +404,60 @@
         <v>0.78400000000000003</v>
       </c>
       <c r="C1">
-        <v>0.58599999999999997</v>
+        <v>0.85299999999999998</v>
       </c>
       <c r="D1">
-        <v>0.79800000000000004</v>
+        <v>0.89300000000000002</v>
       </c>
       <c r="E1">
-        <v>0.84699999999999998</v>
+        <v>0.92</v>
       </c>
       <c r="F1">
-        <v>0.89100000000000001</v>
+        <v>0.93100000000000005</v>
       </c>
       <c r="G1">
-        <v>0.91200000000000003</v>
+        <v>0.95</v>
       </c>
       <c r="H1">
-        <v>0.91200000000000003</v>
+        <v>0.95599999999999996</v>
       </c>
       <c r="I1">
-        <v>0.94499999999999995</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="J1">
-        <v>0.95299999999999996</v>
+        <v>0.96699999999999997</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.49199999999999999</v>
+        <v>0.49299999999999999</v>
       </c>
       <c r="B2">
         <v>0.76</v>
       </c>
       <c r="C2">
-        <v>0.57899999999999996</v>
+        <v>0.84299999999999997</v>
       </c>
       <c r="D2">
-        <v>0.78400000000000003</v>
+        <v>0.88300000000000001</v>
       </c>
       <c r="E2">
-        <v>0.84</v>
+        <v>0.90800000000000003</v>
       </c>
       <c r="F2">
-        <v>0.88200000000000001</v>
+        <v>0.91500000000000004</v>
       </c>
       <c r="G2">
-        <v>0.90800000000000003</v>
+        <v>0.93700000000000006</v>
       </c>
       <c r="H2">
-        <v>0.90500000000000003</v>
+        <v>0.94099999999999995</v>
       </c>
       <c r="I2">
-        <v>0.93500000000000005</v>
+        <v>0.95799999999999996</v>
       </c>
       <c r="J2">
-        <v>0.94099999999999995</v>
+        <v>0.95799999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,13 +468,13 @@
         <v>0.74</v>
       </c>
       <c r="C3">
-        <v>0.84599999999999997</v>
+        <v>0.83099999999999996</v>
       </c>
       <c r="D3">
         <v>0.86499999999999999</v>
       </c>
       <c r="E3">
-        <v>0.90100000000000002</v>
+        <v>0.89900000000000002</v>
       </c>
       <c r="F3">
         <v>0.90900000000000003</v>
@@ -489,21 +489,21 @@
         <v>0.94399999999999995</v>
       </c>
       <c r="J3">
-        <v>0.94899999999999995</v>
+        <v>0.94799999999999995</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.49199999999999999</v>
+        <v>0.46500000000000002</v>
       </c>
       <c r="B4">
-        <v>0.71799999999999997</v>
+        <v>0.70899999999999996</v>
       </c>
       <c r="C4">
-        <v>0.81100000000000005</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="D4">
-        <v>0.85199999999999998</v>
+        <v>0.85299999999999998</v>
       </c>
       <c r="E4">
         <v>0.88</v>
@@ -515,7 +515,7 @@
         <v>0.91100000000000003</v>
       </c>
       <c r="H4">
-        <v>0.90900000000000003</v>
+        <v>0.91</v>
       </c>
       <c r="I4">
         <v>0.93</v>
@@ -558,34 +558,34 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.42099999999999999</v>
+        <v>0.42199999999999999</v>
       </c>
       <c r="B6">
         <v>0.67900000000000005</v>
       </c>
       <c r="C6">
-        <v>0.88</v>
+        <v>0.78500000000000003</v>
       </c>
       <c r="D6">
-        <v>0.86899999999999999</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="E6">
-        <v>0.89300000000000002</v>
+        <v>0.878</v>
       </c>
       <c r="F6">
-        <v>0.9</v>
+        <v>0.89500000000000002</v>
       </c>
       <c r="G6">
-        <v>0.92200000000000004</v>
+        <v>0.91800000000000004</v>
       </c>
       <c r="H6">
-        <v>0.92300000000000004</v>
+        <v>0.91900000000000004</v>
       </c>
       <c r="I6">
-        <v>0.95099999999999996</v>
+        <v>0.95</v>
       </c>
       <c r="J6">
-        <v>0.94599999999999995</v>
+        <v>0.94299999999999995</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,10 +596,10 @@
         <v>0.64200000000000002</v>
       </c>
       <c r="C7">
-        <v>0.75</v>
+        <v>0.754</v>
       </c>
       <c r="D7">
-        <v>0.83</v>
+        <v>0.83099999999999996</v>
       </c>
       <c r="E7">
         <v>0.86399999999999999</v>
@@ -608,7 +608,7 @@
         <v>0.89200000000000002</v>
       </c>
       <c r="G7">
-        <v>0.90800000000000003</v>
+        <v>0.91200000000000003</v>
       </c>
       <c r="H7">
         <v>0.90800000000000003</v>
@@ -622,34 +622,34 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>0.41699999999999998</v>
+        <v>0.41799999999999998</v>
       </c>
       <c r="B8">
         <v>0.746</v>
       </c>
       <c r="C8">
-        <v>0.311</v>
+        <v>0.81499999999999995</v>
       </c>
       <c r="D8">
-        <v>0.72199999999999998</v>
+        <v>0.84899999999999998</v>
       </c>
       <c r="E8">
-        <v>0.79500000000000004</v>
+        <v>0.875</v>
       </c>
       <c r="F8">
-        <v>0.83399999999999996</v>
+        <v>0.9</v>
       </c>
       <c r="G8">
-        <v>0.85499999999999998</v>
+        <v>0.9</v>
       </c>
       <c r="H8">
-        <v>0.86199999999999999</v>
+        <v>0.88900000000000001</v>
       </c>
       <c r="I8">
-        <v>0.85299999999999998</v>
+        <v>0.94</v>
       </c>
       <c r="J8">
-        <v>0.85599999999999998</v>
+        <v>0.93500000000000005</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>0.55800000000000005</v>
       </c>
       <c r="C9">
-        <v>0.73099999999999998</v>
+        <v>0.45</v>
       </c>
       <c r="D9">
-        <v>0.94899999999999995</v>
+        <v>0.39100000000000001</v>
       </c>
       <c r="E9">
-        <v>0.85499999999999998</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="F9">
-        <v>0.60299999999999998</v>
+        <v>0.46400000000000002</v>
       </c>
       <c r="G9">
-        <v>0.56999999999999995</v>
+        <v>0.51</v>
       </c>
       <c r="H9">
-        <v>0.59799999999999998</v>
+        <v>0.56599999999999995</v>
       </c>
       <c r="I9">
-        <v>0.65600000000000003</v>
+        <v>0.622</v>
       </c>
       <c r="J9">
-        <v>0.66</v>
+        <v>0.64600000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/pgroups3.xlsx
+++ b/xlsx/Power/pgroups3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F672E7FF-B853-4818-B0F1-7D5E0709655D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72860D9F-9E78-497D-B4B3-9905C5E54BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4485" yWindow="3945" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{FCA0BD69-1097-4BD5-987D-1F380216A0FD}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{FCA0BD69-1097-4BD5-987D-1F380216A0FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,19 +398,19 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.50900000000000001</v>
+        <v>0.50700000000000001</v>
       </c>
       <c r="B1">
         <v>0.78400000000000003</v>
       </c>
       <c r="C1">
-        <v>0.85299999999999998</v>
+        <v>0.85599999999999998</v>
       </c>
       <c r="D1">
         <v>0.89300000000000002</v>
       </c>
       <c r="E1">
-        <v>0.92</v>
+        <v>0.92100000000000004</v>
       </c>
       <c r="F1">
         <v>0.93100000000000005</v>
@@ -419,24 +419,24 @@
         <v>0.95</v>
       </c>
       <c r="H1">
-        <v>0.95599999999999996</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="I1">
+        <v>0.97</v>
+      </c>
+      <c r="J1">
         <v>0.96799999999999997</v>
-      </c>
-      <c r="J1">
-        <v>0.96699999999999997</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.49299999999999999</v>
+        <v>0.48699999999999999</v>
       </c>
       <c r="B2">
         <v>0.76</v>
       </c>
       <c r="C2">
-        <v>0.84299999999999997</v>
+        <v>0.84399999999999997</v>
       </c>
       <c r="D2">
         <v>0.88300000000000001</v>
@@ -451,21 +451,21 @@
         <v>0.93700000000000006</v>
       </c>
       <c r="H2">
-        <v>0.94099999999999995</v>
+        <v>0.94</v>
       </c>
       <c r="I2">
         <v>0.95799999999999996</v>
       </c>
       <c r="J2">
-        <v>0.95799999999999996</v>
+        <v>0.95899999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.48099999999999998</v>
+        <v>0.47799999999999998</v>
       </c>
       <c r="B3">
-        <v>0.74</v>
+        <v>0.74199999999999999</v>
       </c>
       <c r="C3">
         <v>0.83099999999999996</v>
@@ -474,7 +474,7 @@
         <v>0.86499999999999999</v>
       </c>
       <c r="E3">
-        <v>0.89900000000000002</v>
+        <v>0.90100000000000002</v>
       </c>
       <c r="F3">
         <v>0.90900000000000003</v>
@@ -489,18 +489,18 @@
         <v>0.94399999999999995</v>
       </c>
       <c r="J3">
-        <v>0.94799999999999995</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.46500000000000002</v>
+        <v>0.46100000000000002</v>
       </c>
       <c r="B4">
-        <v>0.70899999999999996</v>
+        <v>0.71199999999999997</v>
       </c>
       <c r="C4">
-        <v>0.80800000000000005</v>
+        <v>0.81</v>
       </c>
       <c r="D4">
         <v>0.85299999999999998</v>
@@ -515,50 +515,50 @@
         <v>0.91100000000000003</v>
       </c>
       <c r="H4">
-        <v>0.91</v>
+        <v>0.91100000000000003</v>
       </c>
       <c r="I4">
-        <v>0.93</v>
+        <v>0.93100000000000005</v>
       </c>
       <c r="J4">
-        <v>0.93600000000000005</v>
+        <v>0.93799999999999994</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0.50700000000000001</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0.57599999999999996</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0.63200000000000001</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0.69499999999999995</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0.73899999999999999</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0.78600000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.42199999999999999</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="B6">
         <v>0.67900000000000005</v>
@@ -570,36 +570,36 @@
         <v>0.84499999999999997</v>
       </c>
       <c r="E6">
-        <v>0.878</v>
+        <v>0.877</v>
       </c>
       <c r="F6">
         <v>0.89500000000000002</v>
       </c>
       <c r="G6">
-        <v>0.91800000000000004</v>
+        <v>0.91500000000000004</v>
       </c>
       <c r="H6">
-        <v>0.91900000000000004</v>
+        <v>0.91400000000000003</v>
       </c>
       <c r="I6">
-        <v>0.95</v>
+        <v>0.94899999999999995</v>
       </c>
       <c r="J6">
-        <v>0.94299999999999995</v>
+        <v>0.94399999999999995</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.38800000000000001</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="B7">
-        <v>0.64200000000000002</v>
+        <v>0.64</v>
       </c>
       <c r="C7">
-        <v>0.754</v>
+        <v>0.753</v>
       </c>
       <c r="D7">
-        <v>0.83099999999999996</v>
+        <v>0.83</v>
       </c>
       <c r="E7">
         <v>0.86399999999999999</v>
@@ -608,7 +608,7 @@
         <v>0.89200000000000002</v>
       </c>
       <c r="G7">
-        <v>0.91200000000000003</v>
+        <v>0.91100000000000003</v>
       </c>
       <c r="H7">
         <v>0.90800000000000003</v>
@@ -625,13 +625,13 @@
         <v>0.41799999999999998</v>
       </c>
       <c r="B8">
-        <v>0.746</v>
+        <v>0.747</v>
       </c>
       <c r="C8">
         <v>0.81499999999999995</v>
       </c>
       <c r="D8">
-        <v>0.84899999999999998</v>
+        <v>0.85099999999999998</v>
       </c>
       <c r="E8">
         <v>0.875</v>
@@ -657,31 +657,31 @@
         <v>0.312</v>
       </c>
       <c r="B9">
-        <v>0.55800000000000005</v>
+        <v>0.56100000000000005</v>
       </c>
       <c r="C9">
-        <v>0.45</v>
+        <v>0.45100000000000001</v>
       </c>
       <c r="D9">
-        <v>0.39100000000000001</v>
+        <v>0.39300000000000002</v>
       </c>
       <c r="E9">
-        <v>0.41699999999999998</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="F9">
-        <v>0.46400000000000002</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="G9">
-        <v>0.51</v>
+        <v>0.50700000000000001</v>
       </c>
       <c r="H9">
-        <v>0.56599999999999995</v>
+        <v>0.56699999999999995</v>
       </c>
       <c r="I9">
-        <v>0.622</v>
+        <v>0.625</v>
       </c>
       <c r="J9">
-        <v>0.64600000000000002</v>
+        <v>0.65200000000000002</v>
       </c>
     </row>
   </sheetData>
